--- a/Processed_Domestic_Granules PWP Sale For Automation.xlsx
+++ b/Processed_Domestic_Granules PWP Sale For Automation.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4390" uniqueCount="590">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4918" uniqueCount="590">
   <si>
     <t>Quantity Sold(MT)</t>
   </si>
@@ -19142,7 +19142,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:S45"/>
+  <dimension ref="A1:S89"/>
   <sheetFormatPr defaultRowHeight="14.25" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.45" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="19.59765625" style="1" customWidth="1"/>
@@ -21551,6 +21551,2338 @@
         <v>28</v>
       </c>
     </row>
+    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A46" s="1">
+        <v>5</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G46" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H46" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I46" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="J46" s="1">
+        <v>39076990</v>
+      </c>
+      <c r="K46" s="1" t="s">
+        <v>506</v>
+      </c>
+      <c r="L46" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M46" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="N46" s="1">
+        <v>612500</v>
+      </c>
+      <c r="O46" s="1">
+        <v>110250</v>
+      </c>
+      <c r="P46" s="2">
+        <v>45748</v>
+      </c>
+      <c r="Q46" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A47" s="1">
+        <v>10</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G47" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H47" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I47" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="J47" s="1">
+        <v>39076990</v>
+      </c>
+      <c r="K47" s="1" t="s">
+        <v>507</v>
+      </c>
+      <c r="L47" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M47" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="N47" s="1">
+        <v>1225000</v>
+      </c>
+      <c r="O47" s="1">
+        <v>220500</v>
+      </c>
+      <c r="P47" s="2">
+        <v>45748</v>
+      </c>
+      <c r="Q47" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A48" s="1">
+        <v>15</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>508</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G48" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H48" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I48" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="J48" s="1">
+        <v>39076990</v>
+      </c>
+      <c r="K48" s="1" t="s">
+        <v>510</v>
+      </c>
+      <c r="L48" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M48" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="N48" s="1">
+        <v>1837500</v>
+      </c>
+      <c r="O48" s="1">
+        <v>330750</v>
+      </c>
+      <c r="P48" s="2">
+        <v>45748</v>
+      </c>
+      <c r="Q48" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A49" s="1">
+        <v>10</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="G49" s="1" t="s">
+        <v>513</v>
+      </c>
+      <c r="H49" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I49" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="J49" s="1">
+        <v>39076990</v>
+      </c>
+      <c r="K49" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="L49" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M49" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="N49" s="1">
+        <v>1215000</v>
+      </c>
+      <c r="O49" s="1">
+        <v>218700</v>
+      </c>
+      <c r="P49" s="2">
+        <v>45773</v>
+      </c>
+      <c r="Q49" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="50" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A50" s="1">
+        <v>5</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="G50" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="H50" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I50" s="1" t="s">
+        <v>518</v>
+      </c>
+      <c r="J50" s="1">
+        <v>39076990</v>
+      </c>
+      <c r="K50" s="1" t="s">
+        <v>519</v>
+      </c>
+      <c r="L50" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M50" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="N50" s="1">
+        <v>590000</v>
+      </c>
+      <c r="O50" s="1">
+        <v>106200</v>
+      </c>
+      <c r="P50" s="2">
+        <v>45785</v>
+      </c>
+      <c r="Q50" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A51" s="1">
+        <v>1</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>521</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G51" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="H51" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I51" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="J51" s="1">
+        <v>39076990</v>
+      </c>
+      <c r="K51" s="1" t="s">
+        <v>523</v>
+      </c>
+      <c r="L51" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M51" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="N51" s="1">
+        <v>145000</v>
+      </c>
+      <c r="O51" s="1">
+        <v>26100</v>
+      </c>
+      <c r="P51" s="2">
+        <v>45791</v>
+      </c>
+      <c r="Q51" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A52" s="1">
+        <v>15</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G52" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H52" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I52" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="J52" s="1">
+        <v>39076990</v>
+      </c>
+      <c r="K52" s="1" t="s">
+        <v>524</v>
+      </c>
+      <c r="L52" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M52" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="N52" s="1">
+        <v>1830000</v>
+      </c>
+      <c r="O52" s="1">
+        <v>329400</v>
+      </c>
+      <c r="P52" s="2">
+        <v>45792</v>
+      </c>
+      <c r="Q52" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A53" s="1">
+        <v>15</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G53" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H53" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I53" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="J53" s="1">
+        <v>39076990</v>
+      </c>
+      <c r="K53" s="1" t="s">
+        <v>525</v>
+      </c>
+      <c r="L53" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M53" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="N53" s="1">
+        <v>1830000</v>
+      </c>
+      <c r="O53" s="1">
+        <v>329400</v>
+      </c>
+      <c r="P53" s="2">
+        <v>45792</v>
+      </c>
+      <c r="Q53" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A54" s="1">
+        <v>5</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="G54" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="H54" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I54" s="1" t="s">
+        <v>518</v>
+      </c>
+      <c r="J54" s="1">
+        <v>39076990</v>
+      </c>
+      <c r="K54" s="1" t="s">
+        <v>526</v>
+      </c>
+      <c r="L54" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M54" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="N54" s="1">
+        <v>575000</v>
+      </c>
+      <c r="O54" s="1">
+        <v>103500</v>
+      </c>
+      <c r="P54" s="2">
+        <v>45821</v>
+      </c>
+      <c r="Q54" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="55" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A55" s="1">
+        <v>5</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="F55" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="G55" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="H55" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I55" s="1" t="s">
+        <v>518</v>
+      </c>
+      <c r="J55" s="1">
+        <v>39076990</v>
+      </c>
+      <c r="K55" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="L55" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M55" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="N55" s="1">
+        <v>575000</v>
+      </c>
+      <c r="O55" s="1">
+        <v>103500</v>
+      </c>
+      <c r="P55" s="2">
+        <v>45835</v>
+      </c>
+      <c r="Q55" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="56" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A56" s="1">
+        <v>10</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="G56" s="1" t="s">
+        <v>513</v>
+      </c>
+      <c r="H56" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I56" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="J56" s="1">
+        <v>39076990</v>
+      </c>
+      <c r="K56" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="L56" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M56" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="N56" s="1">
+        <v>1165000</v>
+      </c>
+      <c r="O56" s="1">
+        <v>209700</v>
+      </c>
+      <c r="P56" s="2">
+        <v>45841</v>
+      </c>
+      <c r="Q56" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A57" s="1">
+        <v>1</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="G57" s="1" t="s">
+        <v>531</v>
+      </c>
+      <c r="H57" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I57" s="1" t="s">
+        <v>532</v>
+      </c>
+      <c r="J57" s="1">
+        <v>39076990</v>
+      </c>
+      <c r="K57" s="1" t="s">
+        <v>533</v>
+      </c>
+      <c r="L57" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M57" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="N57" s="1">
+        <v>153000</v>
+      </c>
+      <c r="O57" s="1">
+        <v>27540</v>
+      </c>
+      <c r="P57" s="2">
+        <v>45877</v>
+      </c>
+      <c r="Q57" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="58" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A58" s="1">
+        <v>5</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>535</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="G58" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H58" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I58" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="J58" s="1">
+        <v>39076990</v>
+      </c>
+      <c r="K58" s="1" t="s">
+        <v>537</v>
+      </c>
+      <c r="L58" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M58" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="N58" s="1">
+        <v>575000</v>
+      </c>
+      <c r="O58" s="1">
+        <v>103500</v>
+      </c>
+      <c r="P58" s="2">
+        <v>45877</v>
+      </c>
+      <c r="Q58" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="59" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A59" s="1">
+        <v>5</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="E59" s="1" t="s">
+        <v>521</v>
+      </c>
+      <c r="F59" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G59" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="H59" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I59" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="J59" s="1">
+        <v>39076990</v>
+      </c>
+      <c r="K59" s="1" t="s">
+        <v>538</v>
+      </c>
+      <c r="L59" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M59" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="N59" s="1">
+        <v>570000</v>
+      </c>
+      <c r="O59" s="1">
+        <v>102600</v>
+      </c>
+      <c r="P59" s="2">
+        <v>45881</v>
+      </c>
+      <c r="Q59" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="60" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A60" s="1">
+        <v>6</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="G60" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="H60" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I60" s="1" t="s">
+        <v>518</v>
+      </c>
+      <c r="J60" s="1">
+        <v>39076990</v>
+      </c>
+      <c r="K60" s="1" t="s">
+        <v>539</v>
+      </c>
+      <c r="L60" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M60" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="N60" s="1">
+        <v>690000</v>
+      </c>
+      <c r="O60" s="1">
+        <v>124200</v>
+      </c>
+      <c r="P60" s="2">
+        <v>45882</v>
+      </c>
+      <c r="Q60" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="61" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A61" s="1">
+        <v>3</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>535</v>
+      </c>
+      <c r="F61" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="G61" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H61" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I61" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="J61" s="1">
+        <v>39076990</v>
+      </c>
+      <c r="K61" s="1" t="s">
+        <v>540</v>
+      </c>
+      <c r="L61" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M61" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="N61" s="1">
+        <v>345000</v>
+      </c>
+      <c r="O61" s="1">
+        <v>62100</v>
+      </c>
+      <c r="P61" s="2">
+        <v>45888</v>
+      </c>
+      <c r="Q61" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="62" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A62" s="1">
+        <v>5</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="E62" s="1" t="s">
+        <v>521</v>
+      </c>
+      <c r="F62" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G62" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="H62" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I62" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="J62" s="1">
+        <v>39076990</v>
+      </c>
+      <c r="K62" s="1" t="s">
+        <v>541</v>
+      </c>
+      <c r="L62" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M62" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="N62" s="1">
+        <v>570000</v>
+      </c>
+      <c r="O62" s="1">
+        <v>102600</v>
+      </c>
+      <c r="P62" s="2">
+        <v>45894</v>
+      </c>
+      <c r="Q62" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="63" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A63" s="1">
+        <v>5</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="F63" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="G63" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="H63" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I63" s="1" t="s">
+        <v>518</v>
+      </c>
+      <c r="J63" s="1">
+        <v>39076990</v>
+      </c>
+      <c r="K63" s="1" t="s">
+        <v>542</v>
+      </c>
+      <c r="L63" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M63" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="N63" s="1">
+        <v>575000</v>
+      </c>
+      <c r="O63" s="1">
+        <v>103500</v>
+      </c>
+      <c r="P63" s="2">
+        <v>45900</v>
+      </c>
+      <c r="Q63" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="64" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A64" s="1">
+        <v>5</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>521</v>
+      </c>
+      <c r="F64" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G64" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="H64" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I64" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="J64" s="1">
+        <v>39076990</v>
+      </c>
+      <c r="K64" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="L64" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M64" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="N64" s="1">
+        <v>575000</v>
+      </c>
+      <c r="O64" s="1">
+        <v>103500</v>
+      </c>
+      <c r="P64" s="2">
+        <v>45911</v>
+      </c>
+      <c r="Q64" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="65" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A65" s="1">
+        <v>5</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="E65" s="1" t="s">
+        <v>521</v>
+      </c>
+      <c r="F65" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G65" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="H65" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I65" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="J65" s="1">
+        <v>39076990</v>
+      </c>
+      <c r="K65" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="L65" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M65" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="N65" s="1">
+        <v>547500</v>
+      </c>
+      <c r="O65" s="1">
+        <v>98550</v>
+      </c>
+      <c r="P65" s="2">
+        <v>45940</v>
+      </c>
+      <c r="Q65" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="66" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A66" s="1">
+        <v>10</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="E66" s="1" t="s">
+        <v>521</v>
+      </c>
+      <c r="F66" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G66" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="H66" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I66" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="J66" s="1">
+        <v>39076990</v>
+      </c>
+      <c r="K66" s="1" t="s">
+        <v>545</v>
+      </c>
+      <c r="L66" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M66" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="N66" s="1">
+        <v>1090000</v>
+      </c>
+      <c r="O66" s="1">
+        <v>196200</v>
+      </c>
+      <c r="P66" s="2">
+        <v>45955</v>
+      </c>
+      <c r="Q66" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="67" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A67" s="1">
+        <v>5</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="E67" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="F67" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="G67" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="H67" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I67" s="1" t="s">
+        <v>518</v>
+      </c>
+      <c r="J67" s="1">
+        <v>39076990</v>
+      </c>
+      <c r="K67" s="1" t="s">
+        <v>546</v>
+      </c>
+      <c r="L67" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M67" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="N67" s="1">
+        <v>527500</v>
+      </c>
+      <c r="O67" s="1">
+        <v>94950</v>
+      </c>
+      <c r="P67" s="2">
+        <v>45974</v>
+      </c>
+      <c r="Q67" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="68" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A68" s="1">
+        <v>10</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="E68" s="1" t="s">
+        <v>521</v>
+      </c>
+      <c r="F68" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G68" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="H68" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I68" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="J68" s="1">
+        <v>39076990</v>
+      </c>
+      <c r="K68" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="L68" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M68" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="N68" s="1">
+        <v>1070000</v>
+      </c>
+      <c r="O68" s="1">
+        <v>192600</v>
+      </c>
+      <c r="P68" s="2">
+        <v>45979</v>
+      </c>
+      <c r="Q68" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="69" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A69" s="1">
+        <v>10</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="E69" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="F69" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="G69" s="1" t="s">
+        <v>513</v>
+      </c>
+      <c r="H69" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I69" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="J69" s="1">
+        <v>39076990</v>
+      </c>
+      <c r="K69" s="1" t="s">
+        <v>548</v>
+      </c>
+      <c r="L69" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M69" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="N69" s="1">
+        <v>1020000</v>
+      </c>
+      <c r="O69" s="1">
+        <v>183600</v>
+      </c>
+      <c r="P69" s="2">
+        <v>46006</v>
+      </c>
+      <c r="Q69" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="70" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A70" s="1">
+        <v>5</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D70" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="E70" s="1" t="s">
+        <v>521</v>
+      </c>
+      <c r="F70" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G70" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="H70" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I70" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="J70" s="1">
+        <v>39076990</v>
+      </c>
+      <c r="K70" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="L70" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M70" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="N70" s="1">
+        <v>520000</v>
+      </c>
+      <c r="O70" s="1">
+        <v>93600</v>
+      </c>
+      <c r="P70" s="2">
+        <v>46011</v>
+      </c>
+      <c r="Q70" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="71" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A71" s="1">
+        <v>5</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="E71" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="F71" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="G71" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="H71" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I71" s="1" t="s">
+        <v>518</v>
+      </c>
+      <c r="J71" s="1">
+        <v>39076990</v>
+      </c>
+      <c r="K71" s="1" t="s">
+        <v>550</v>
+      </c>
+      <c r="L71" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M71" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="N71" s="1">
+        <v>517500</v>
+      </c>
+      <c r="O71" s="1">
+        <v>93150</v>
+      </c>
+      <c r="P71" s="2">
+        <v>46012</v>
+      </c>
+      <c r="Q71" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="72" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A72" s="1">
+        <v>20</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="E72" s="1" t="s">
+        <v>535</v>
+      </c>
+      <c r="F72" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="G72" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H72" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I72" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="J72" s="1">
+        <v>39076990</v>
+      </c>
+      <c r="K72" s="1" t="s">
+        <v>551</v>
+      </c>
+      <c r="L72" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M72" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="N72" s="1">
+        <v>2090000</v>
+      </c>
+      <c r="O72" s="1">
+        <v>376200</v>
+      </c>
+      <c r="P72" s="2">
+        <v>46046</v>
+      </c>
+      <c r="Q72" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="73" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A73" s="1">
+        <v>20</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D73" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="E73" s="1" t="s">
+        <v>535</v>
+      </c>
+      <c r="F73" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="G73" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H73" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I73" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="J73" s="1">
+        <v>39076990</v>
+      </c>
+      <c r="K73" s="1" t="s">
+        <v>552</v>
+      </c>
+      <c r="L73" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M73" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="N73" s="1">
+        <v>2090000</v>
+      </c>
+      <c r="O73" s="1">
+        <v>376200</v>
+      </c>
+      <c r="P73" s="2">
+        <v>46047</v>
+      </c>
+      <c r="Q73" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="74" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A74" s="1">
+        <v>10</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="E74" s="1" t="s">
+        <v>521</v>
+      </c>
+      <c r="F74" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G74" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="H74" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I74" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="J74" s="1">
+        <v>39076990</v>
+      </c>
+      <c r="K74" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="L74" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M74" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="N74" s="1">
+        <v>1085000</v>
+      </c>
+      <c r="O74" s="1">
+        <v>195300</v>
+      </c>
+      <c r="P74" s="2">
+        <v>46063</v>
+      </c>
+      <c r="Q74" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="75" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A75" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>554</v>
+      </c>
+      <c r="E75" s="1" t="s">
+        <v>555</v>
+      </c>
+      <c r="F75" s="1" t="s">
+        <v>556</v>
+      </c>
+      <c r="G75" s="1" t="s">
+        <v>557</v>
+      </c>
+      <c r="H75" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I75" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="J75" s="1">
+        <v>39076990</v>
+      </c>
+      <c r="K75" s="1" t="s">
+        <v>559</v>
+      </c>
+      <c r="L75" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M75" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="N75" s="1">
+        <v>6750</v>
+      </c>
+      <c r="O75" s="1">
+        <v>1215</v>
+      </c>
+      <c r="P75" s="2">
+        <v>46065</v>
+      </c>
+      <c r="Q75" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="76" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A76" s="1">
+        <v>1</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D76" s="1" t="s">
+        <v>560</v>
+      </c>
+      <c r="E76" s="1" t="s">
+        <v>561</v>
+      </c>
+      <c r="F76" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="G76" s="1" t="s">
+        <v>562</v>
+      </c>
+      <c r="H76" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I76" s="1" t="s">
+        <v>563</v>
+      </c>
+      <c r="J76" s="1">
+        <v>39076990</v>
+      </c>
+      <c r="K76" s="1" t="s">
+        <v>564</v>
+      </c>
+      <c r="L76" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M76" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="N76" s="1">
+        <v>116000</v>
+      </c>
+      <c r="O76" s="1">
+        <v>20880</v>
+      </c>
+      <c r="P76" s="2">
+        <v>46070</v>
+      </c>
+      <c r="Q76" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="77" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A77" s="1">
+        <v>20</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D77" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="E77" s="1" t="s">
+        <v>535</v>
+      </c>
+      <c r="F77" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="G77" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H77" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I77" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="J77" s="1">
+        <v>39076990</v>
+      </c>
+      <c r="K77" s="1" t="s">
+        <v>565</v>
+      </c>
+      <c r="L77" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M77" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="N77" s="1">
+        <v>2100000</v>
+      </c>
+      <c r="O77" s="1">
+        <v>378000</v>
+      </c>
+      <c r="P77" s="2">
+        <v>46086</v>
+      </c>
+      <c r="Q77" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="78" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A78" s="1">
+        <v>30</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D78" s="1" t="s">
+        <v>566</v>
+      </c>
+      <c r="E78" s="1" t="s">
+        <v>567</v>
+      </c>
+      <c r="F78" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G78" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H78" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I78" s="1" t="s">
+        <v>568</v>
+      </c>
+      <c r="J78" s="1">
+        <v>39076990</v>
+      </c>
+      <c r="K78" s="1" t="s">
+        <v>569</v>
+      </c>
+      <c r="L78" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M78" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="N78" s="1">
+        <v>3480000</v>
+      </c>
+      <c r="O78" s="1">
+        <v>626400</v>
+      </c>
+      <c r="P78" s="2">
+        <v>46092</v>
+      </c>
+      <c r="Q78" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="79" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A79" s="1">
+        <v>20</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>566</v>
+      </c>
+      <c r="E79" s="1" t="s">
+        <v>567</v>
+      </c>
+      <c r="F79" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G79" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H79" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I79" s="1" t="s">
+        <v>568</v>
+      </c>
+      <c r="J79" s="1">
+        <v>39076990</v>
+      </c>
+      <c r="K79" s="1" t="s">
+        <v>570</v>
+      </c>
+      <c r="L79" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M79" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="N79" s="1">
+        <v>2320000</v>
+      </c>
+      <c r="O79" s="1">
+        <v>417600</v>
+      </c>
+      <c r="P79" s="2">
+        <v>46092</v>
+      </c>
+      <c r="Q79" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="80" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A80" s="1">
+        <v>5</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D80" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="E80" s="1" t="s">
+        <v>521</v>
+      </c>
+      <c r="F80" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G80" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="H80" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I80" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="J80" s="1">
+        <v>39076990</v>
+      </c>
+      <c r="K80" s="1" t="s">
+        <v>571</v>
+      </c>
+      <c r="L80" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M80" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="N80" s="1">
+        <v>590000</v>
+      </c>
+      <c r="O80" s="1">
+        <v>106200</v>
+      </c>
+      <c r="P80" s="2">
+        <v>46095</v>
+      </c>
+      <c r="Q80" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="81" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A81" s="1">
+        <v>0.25</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D81" s="1" t="s">
+        <v>572</v>
+      </c>
+      <c r="E81" s="1" t="s">
+        <v>573</v>
+      </c>
+      <c r="F81" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="G81" s="1" t="s">
+        <v>574</v>
+      </c>
+      <c r="H81" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I81" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="J81" s="1">
+        <v>39076990</v>
+      </c>
+      <c r="K81" s="1" t="s">
+        <v>576</v>
+      </c>
+      <c r="L81" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M81" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="N81" s="1">
+        <v>30000</v>
+      </c>
+      <c r="O81" s="1">
+        <v>5400</v>
+      </c>
+      <c r="P81" s="2">
+        <v>46101</v>
+      </c>
+      <c r="Q81" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="82" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A82" s="1">
+        <v>7</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D82" s="1" t="s">
+        <v>577</v>
+      </c>
+      <c r="E82" s="1" t="s">
+        <v>578</v>
+      </c>
+      <c r="F82" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="G82" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="H82" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I82" s="1" t="s">
+        <v>579</v>
+      </c>
+      <c r="J82" s="1">
+        <v>39076990</v>
+      </c>
+      <c r="K82" s="1" t="s">
+        <v>580</v>
+      </c>
+      <c r="L82" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M82" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="N82" s="1">
+        <v>815500</v>
+      </c>
+      <c r="O82" s="1">
+        <v>146790</v>
+      </c>
+      <c r="P82" s="2">
+        <v>46102</v>
+      </c>
+      <c r="Q82" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="83" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A83" s="1">
+        <v>20</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D83" s="1" t="s">
+        <v>566</v>
+      </c>
+      <c r="E83" s="1" t="s">
+        <v>567</v>
+      </c>
+      <c r="F83" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G83" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H83" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I83" s="1" t="s">
+        <v>568</v>
+      </c>
+      <c r="J83" s="1">
+        <v>39076990</v>
+      </c>
+      <c r="K83" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="L83" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M83" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="N83" s="1">
+        <v>2400000</v>
+      </c>
+      <c r="O83" s="1">
+        <v>432000</v>
+      </c>
+      <c r="P83" s="2">
+        <v>46106</v>
+      </c>
+      <c r="Q83" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="84" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A84" s="1">
+        <v>5</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D84" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="E84" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="F84" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="G84" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="H84" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I84" s="1" t="s">
+        <v>518</v>
+      </c>
+      <c r="J84" s="1">
+        <v>39076990</v>
+      </c>
+      <c r="K84" s="1" t="s">
+        <v>582</v>
+      </c>
+      <c r="L84" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M84" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="N84" s="1">
+        <v>580000</v>
+      </c>
+      <c r="O84" s="1">
+        <v>104400</v>
+      </c>
+      <c r="P84" s="2">
+        <v>46106</v>
+      </c>
+      <c r="Q84" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="85" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A85" s="1">
+        <v>15</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D85" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="E85" s="1" t="s">
+        <v>583</v>
+      </c>
+      <c r="F85" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G85" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="H85" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I85" s="1" t="s">
+        <v>584</v>
+      </c>
+      <c r="J85" s="1">
+        <v>39076990</v>
+      </c>
+      <c r="K85" s="1" t="s">
+        <v>585</v>
+      </c>
+      <c r="L85" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M85" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="N85" s="1">
+        <v>1732500</v>
+      </c>
+      <c r="O85" s="1">
+        <v>311850</v>
+      </c>
+      <c r="P85" s="2">
+        <v>46107</v>
+      </c>
+      <c r="Q85" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="86" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A86" s="1">
+        <v>30</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D86" s="1" t="s">
+        <v>566</v>
+      </c>
+      <c r="E86" s="1" t="s">
+        <v>567</v>
+      </c>
+      <c r="F86" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G86" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H86" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I86" s="1" t="s">
+        <v>568</v>
+      </c>
+      <c r="J86" s="1">
+        <v>39076990</v>
+      </c>
+      <c r="K86" s="1" t="s">
+        <v>586</v>
+      </c>
+      <c r="L86" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M86" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="N86" s="1">
+        <v>3600000</v>
+      </c>
+      <c r="O86" s="1">
+        <v>648000</v>
+      </c>
+      <c r="P86" s="2">
+        <v>46109</v>
+      </c>
+      <c r="Q86" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="87" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A87" s="1">
+        <v>15</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D87" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="E87" s="1" t="s">
+        <v>583</v>
+      </c>
+      <c r="F87" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G87" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="H87" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I87" s="1" t="s">
+        <v>584</v>
+      </c>
+      <c r="J87" s="1">
+        <v>39076990</v>
+      </c>
+      <c r="K87" s="1" t="s">
+        <v>587</v>
+      </c>
+      <c r="L87" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M87" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="N87" s="1">
+        <v>1732500</v>
+      </c>
+      <c r="O87" s="1">
+        <v>311850</v>
+      </c>
+      <c r="P87" s="2">
+        <v>46112</v>
+      </c>
+      <c r="Q87" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="88" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A88" s="1">
+        <v>15</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D88" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="E88" s="1" t="s">
+        <v>583</v>
+      </c>
+      <c r="F88" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G88" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="H88" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I88" s="1" t="s">
+        <v>584</v>
+      </c>
+      <c r="J88" s="1">
+        <v>39076990</v>
+      </c>
+      <c r="K88" s="1" t="s">
+        <v>588</v>
+      </c>
+      <c r="L88" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M88" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="N88" s="1">
+        <v>1755000</v>
+      </c>
+      <c r="O88" s="1">
+        <v>315900</v>
+      </c>
+      <c r="P88" s="2">
+        <v>46112</v>
+      </c>
+      <c r="Q88" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="89" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A89" s="1">
+        <v>6</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D89" s="1" t="s">
+        <v>577</v>
+      </c>
+      <c r="E89" s="1" t="s">
+        <v>578</v>
+      </c>
+      <c r="F89" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="G89" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="H89" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I89" s="1" t="s">
+        <v>579</v>
+      </c>
+      <c r="J89" s="1">
+        <v>39076990</v>
+      </c>
+      <c r="K89" s="1" t="s">
+        <v>589</v>
+      </c>
+      <c r="L89" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M89" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="N89" s="1">
+        <v>726000</v>
+      </c>
+      <c r="O89" s="1">
+        <v>130680</v>
+      </c>
+      <c r="P89" s="2">
+        <v>46112</v>
+      </c>
+      <c r="Q89" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
